--- a/testData/loginData.xlsx
+++ b/testData/loginData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salin\Documents\AutomationPractice\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C003C353-4DD0-4807-AB11-D188921B4CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D056CAC2-62E0-4838-8869-AD14B92E65E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginTestData" sheetId="1" r:id="rId1"/>
@@ -25,15 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
     <t>emailAddress</t>
   </si>
   <si>
     <t>password</t>
-  </si>
-  <si>
-    <t>example@gmail.com</t>
   </si>
   <si>
     <t>repano2553@hopesx.com</t>
@@ -388,19 +385,13 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
+      <c r="A3" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{CAA6DFB0-492A-4225-AFE0-8FAFBD287A36}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{2F86A55A-4868-4A8D-8C7D-F1C2CDCBE6A5}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{7E48BEEE-2BD6-4763-AC0F-F9FF99554051}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>